--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -518,7 +518,7 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101215520757100</v>
+        <v>0101215520757101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,12 +521,104 @@
         <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16" t="str">
+        <v>863_干花文竹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>435_猫眼_Echinacea_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7</v>
+      </c>
+      <c r="C20" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +673,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101215520757101</v>
+        <v>01012155207571010201001001002030510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -615,6 +615,9 @@
       <c r="C21" t="str">
         <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -673,7 +676,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01012155207571010201001001002030510100</v>
+        <v>01012155207571010201001001002030510101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -616,12 +616,36 @@
         <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -676,7 +700,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01012155207571010201001001002030510101</v>
+        <v>010121552075710102010010010020305101015201030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,74 +443,77 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+        <v>885_杨梅树枝_undefined_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
       <c r="C3" t="str">
-        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
       <c r="F4" t="str">
-        <v>15</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>259_诺拉_Nora_Rosa rugosa Thunb._10stems</v>
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>707_永生吊米白_undefined_undefined_1bunch</v>
+        <v>637_干花小盼草红_undefined_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="str">
-        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
       </c>
       <c r="F8" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>169_欢乐颂_Silantoi_Rosa rugosa Thunb._20stems</v>
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
       <c r="F9" t="str">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
       </c>
       <c r="F10" t="str">
         <v>10</v>
@@ -518,75 +521,72 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="str">
-        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+        <v>389_金合欢_mimosa_undefined_1bunch</v>
       </c>
       <c r="F12" t="str">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>462_五针松_undefined_undefined_1bunch</v>
       </c>
       <c r="F13" t="str">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>4</v>
-      </c>
       <c r="C14" t="str">
-        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F14" t="str">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="C15" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>5</v>
       </c>
-      <c r="C15" t="str">
-        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F15" t="str">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
+      <c r="C17" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>6</v>
       </c>
-      <c r="C16" t="str">
-        <v>863_干花文竹白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="str">
+      <c r="C18" t="str">
         <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F17" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>435_猫眼_Echinacea_undefined_1bunch</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="19">
       <c r="C19" t="str">
-        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
       </c>
       <c r="F19" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -605,47 +605,263 @@
         <v>7</v>
       </c>
       <c r="C20" t="str">
-        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
       </c>
       <c r="F20" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="str">
-        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="str">
-        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+        <v>444_喜树果_Camptotheca acuminate Decne_undefined_1bunch</v>
       </c>
       <c r="F22" t="str">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="str">
-        <v>388_大丽花_dahlia_undefined_1bunch</v>
+        <v>729_老人须_undefined_undefined_1bunch</v>
       </c>
       <c r="F23" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>8</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>191_朱小姐_Miss Piggy_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>165_杏仁酒_Amaretto_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2</v>
+      </c>
+      <c r="C34" t="str">
+        <v>195_闺蜜_Alter Ego_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>3</v>
+      </c>
+      <c r="C39" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>104_绣球重瓣紫_Hydrangea Purple D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F41" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>105_绣球莫奈蓝_Hydrangea Monet Blue_Hydrangea L._1stem</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>451_景天_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>779_景天绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>382_绿朱蕉_Cordyline Snow White Green_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>4</v>
+      </c>
+      <c r="C48" t="str">
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F48" t="str">
         <v>30</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -700,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010121552075710102010010010020305101015201030</v>
+        <v>07101451510151549102050252511105551510815152110855772410861515530102010301055103015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-29.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-29.xlsx
@@ -918,6 +918,9 @@
       <c r="G2" t="str">
         <v>07101451510151549102050252511105551510815152110855772410861515530102010301055103015</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
